--- a/artfynd/A 19783-2024 artfynd.xlsx
+++ b/artfynd/A 19783-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127034781</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127034759</v>
+        <v>127034782</v>
       </c>
       <c r="B3" t="n">
-        <v>56840</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533371</v>
+        <v>533151</v>
       </c>
       <c r="R3" t="n">
-        <v>6761440</v>
+        <v>6761600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127034782</v>
+        <v>127034759</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>56840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533151</v>
+        <v>533371</v>
       </c>
       <c r="R4" t="n">
-        <v>6761600</v>
+        <v>6761440</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
